--- a/resources/report/60/95/einvoices_template/ParisVN_CNHN/ParisVN_CNHN_1.xlsx
+++ b/resources/report/60/95/einvoices_template/ParisVN_CNHN/ParisVN_CNHN_1.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project's Resources\gsf20\resources\report\60\95\einvoices_template\ParisVN_CNHN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\einvoices_template\ParisVN_CNHN\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="5490"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="5496"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice_PA.18" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="Z_9B1DEEE8_4943_4C9B_AD04_3FBB81BB847B_.wvu.Cols" localSheetId="0" hidden="1">Invoice_PA.18!$L:$L,Invoice_PA.18!#REF!</definedName>
     <definedName name="Z_9B1DEEE8_4943_4C9B_AD04_3FBB81BB847B_.wvu.Rows" localSheetId="0" hidden="1">Invoice_PA.18!#REF!,Invoice_PA.18!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -621,7 +621,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;[Red]#,##0"/>
@@ -1335,7 +1335,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1376,10 +1376,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1396,7 +1392,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1425,10 +1420,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1458,12 +1449,13 @@
     <xf numFmtId="0" fontId="32" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1476,6 +1468,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1488,6 +1486,105 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1509,14 +1606,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -1530,110 +1630,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -1956,70 +1955,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="44" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="44" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="44" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="44" customWidth="1"/>
-    <col min="5" max="5" width="2" style="44" customWidth="1"/>
-    <col min="6" max="6" width="3.140625" style="44" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" style="44" customWidth="1"/>
-    <col min="8" max="8" width="3.42578125" style="44" customWidth="1"/>
-    <col min="9" max="9" width="1.28515625" style="44" customWidth="1"/>
-    <col min="10" max="10" width="1.140625" style="44" customWidth="1"/>
-    <col min="11" max="11" width="6.5703125" style="44" customWidth="1"/>
-    <col min="12" max="12" width="1.42578125" style="44" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="0.28515625" style="44" customWidth="1"/>
-    <col min="14" max="14" width="4" style="44" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" style="44" customWidth="1"/>
-    <col min="16" max="16" width="0.28515625" style="44" customWidth="1"/>
-    <col min="17" max="17" width="4" style="44" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" style="44" customWidth="1"/>
-    <col min="19" max="19" width="0.28515625" style="44" customWidth="1"/>
-    <col min="20" max="20" width="2.7109375" style="44" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="44" customWidth="1"/>
-    <col min="22" max="22" width="0.140625" style="44" customWidth="1"/>
-    <col min="23" max="23" width="4" style="44" customWidth="1"/>
-    <col min="24" max="24" width="4.140625" style="44" customWidth="1"/>
-    <col min="25" max="25" width="6.42578125" style="44" customWidth="1"/>
-    <col min="26" max="26" width="0.140625" style="44" customWidth="1"/>
-    <col min="27" max="27" width="2.85546875" style="44" customWidth="1"/>
-    <col min="28" max="28" width="0.140625" style="44" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="44"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="5" width="2" customWidth="1"/>
+    <col min="6" max="6" width="3.109375" customWidth="1"/>
+    <col min="7" max="7" width="1.88671875" customWidth="1"/>
+    <col min="8" max="8" width="3.44140625" customWidth="1"/>
+    <col min="9" max="9" width="1.33203125" customWidth="1"/>
+    <col min="10" max="10" width="1.109375" customWidth="1"/>
+    <col min="11" max="11" width="6.5546875" customWidth="1"/>
+    <col min="12" max="12" width="1.44140625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="0.33203125" customWidth="1"/>
+    <col min="14" max="14" width="4" customWidth="1"/>
+    <col min="15" max="15" width="5.44140625" customWidth="1"/>
+    <col min="16" max="16" width="0.33203125" customWidth="1"/>
+    <col min="17" max="17" width="4" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="19" max="19" width="0.33203125" customWidth="1"/>
+    <col min="20" max="20" width="2.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="22" max="22" width="0.109375" customWidth="1"/>
+    <col min="23" max="23" width="4" customWidth="1"/>
+    <col min="24" max="24" width="4.109375" customWidth="1"/>
+    <col min="25" max="25" width="6.44140625" customWidth="1"/>
+    <col min="26" max="26" width="0.109375" customWidth="1"/>
+    <col min="27" max="27" width="2.88671875" customWidth="1"/>
+    <col min="28" max="28" width="0.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="16.5" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="16.5" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21"/>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
-      <c r="K1" s="86"/>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="86"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
+      <c r="Y1" s="91"/>
       <c r="Z1" s="22"/>
-      <c r="AA1" s="34"/>
+      <c r="AA1" s="108"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2046,47 +2044,47 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="24"/>
+      <c r="AA2" s="109"/>
       <c r="AB2" s="1"/>
     </row>
-    <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="115"/>
-      <c r="T3" s="115"/>
-      <c r="U3" s="115"/>
-      <c r="V3" s="114"/>
-      <c r="W3" s="114"/>
-      <c r="X3" s="114"/>
-      <c r="Y3" s="114"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
+      <c r="L3" s="79"/>
+      <c r="M3" s="79"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="56"/>
+      <c r="Y3" s="56"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="24"/>
+      <c r="AA3" s="109"/>
       <c r="AB3" s="1"/>
     </row>
-    <row r="4" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
-      <c r="B4" s="115" t="s">
+      <c r="B4" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="115"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="116"/>
       <c r="E4" s="116"/>
       <c r="F4" s="116"/>
@@ -2110,210 +2108,210 @@
       <c r="X4" s="116"/>
       <c r="Y4" s="116"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="24"/>
+      <c r="AA4" s="109"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14"/>
-      <c r="B5" s="114" t="s">
+      <c r="B5" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="117" t="s">
+      <c r="C5" s="56"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="117"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="115"/>
-      <c r="S5" s="115"/>
-      <c r="T5" s="115"/>
-      <c r="U5" s="115"/>
-      <c r="V5" s="114"/>
-      <c r="W5" s="114"/>
-      <c r="X5" s="114"/>
-      <c r="Y5" s="114"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="79"/>
+      <c r="U5" s="79"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="24"/>
+      <c r="AA5" s="109"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118"/>
-      <c r="N6" s="118"/>
-      <c r="O6" s="119" t="s">
+      <c r="C6" s="57"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="118"/>
-      <c r="T6" s="118"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="111"/>
+      <c r="T6" s="111"/>
+      <c r="U6" s="111"/>
+      <c r="V6" s="111"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
       <c r="Z6" s="20"/>
-      <c r="AA6" s="16"/>
+      <c r="AA6" s="110"/>
       <c r="AB6" s="1"/>
     </row>
-    <row r="7" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="101"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="101"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="79"/>
-      <c r="T7" s="79"/>
-      <c r="U7" s="79"/>
-      <c r="V7" s="79"/>
-      <c r="W7" s="79"/>
-      <c r="X7" s="79"/>
-      <c r="Y7" s="79"/>
-      <c r="Z7" s="79"/>
-      <c r="AA7" s="24"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
+      <c r="X7" s="82"/>
+      <c r="Y7" s="82"/>
+      <c r="Z7" s="82"/>
+      <c r="AA7" s="108"/>
       <c r="AB7" s="1"/>
     </row>
-    <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="99" t="s">
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87"/>
+      <c r="M8" s="87"/>
+      <c r="N8" s="87"/>
+      <c r="O8" s="87"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="87"/>
+      <c r="S8" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="T8" s="99"/>
-      <c r="U8" s="99"/>
-      <c r="V8" s="99"/>
-      <c r="W8" s="100"/>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="24"/>
+      <c r="T8" s="88"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="89"/>
+      <c r="X8" s="89"/>
+      <c r="Y8" s="89"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="109"/>
       <c r="AB8" s="1"/>
     </row>
-    <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="79" t="s">
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="79"/>
-      <c r="U9" s="79"/>
-      <c r="V9" s="97"/>
-      <c r="W9" s="97"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="97"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="24"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="86"/>
+      <c r="W9" s="86"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="86"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="109"/>
       <c r="AB9" s="1"/>
     </row>
-    <row r="10" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="71"/>
-      <c r="Q10" s="71"/>
-      <c r="R10" s="71"/>
-      <c r="S10" s="96" t="s">
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
+      <c r="S10" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="96"/>
-      <c r="U10" s="96"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="96"/>
-      <c r="X10" s="96"/>
-      <c r="Y10" s="96"/>
+      <c r="T10" s="85"/>
+      <c r="U10" s="85"/>
+      <c r="V10" s="85"/>
+      <c r="W10" s="85"/>
+      <c r="X10" s="85"/>
+      <c r="Y10" s="85"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="24"/>
+      <c r="AA10" s="109"/>
       <c r="AB10" s="1"/>
     </row>
-    <row r="11" spans="1:28" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2340,200 +2338,202 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="24"/>
+      <c r="AA11" s="109"/>
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
-      <c r="T12" s="79"/>
-      <c r="U12" s="79"/>
-      <c r="V12" s="79"/>
-      <c r="W12" s="79"/>
-      <c r="X12" s="79"/>
-      <c r="Y12" s="79"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="24"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="109"/>
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
-      <c r="R13" s="78"/>
-      <c r="S13" s="78"/>
-      <c r="T13" s="78"/>
-      <c r="U13" s="78"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
-      <c r="X13" s="78"/>
-      <c r="Y13" s="78"/>
-      <c r="Z13" s="78"/>
-      <c r="AA13" s="24"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="84"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
+      <c r="W13" s="84"/>
+      <c r="X13" s="84"/>
+      <c r="Y13" s="84"/>
+      <c r="Z13" s="84"/>
+      <c r="AA13" s="109"/>
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="77"/>
-      <c r="K14" s="77"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="77"/>
-      <c r="O14" s="77"/>
-      <c r="P14" s="77"/>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="26"/>
-      <c r="AA14" s="24"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="83"/>
+      <c r="U14" s="83"/>
+      <c r="V14" s="83"/>
+      <c r="W14" s="83"/>
+      <c r="X14" s="83"/>
+      <c r="Y14" s="83"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="109"/>
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="24"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="109"/>
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="36"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="36"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="24"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="109"/>
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="43" t="s">
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="82"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="79"/>
-      <c r="V17" s="79"/>
-      <c r="W17" s="79"/>
-      <c r="X17" s="79"/>
-      <c r="Y17" s="79"/>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="24"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="40"/>
+      <c r="S17" s="40"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="82"/>
+      <c r="V17" s="82"/>
+      <c r="W17" s="82"/>
+      <c r="X17" s="82"/>
+      <c r="Y17" s="82"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="109"/>
       <c r="AB17" s="1"/>
     </row>
-    <row r="18" spans="1:28" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2560,254 +2560,254 @@
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
-      <c r="AA18" s="24"/>
+      <c r="AA18" s="109"/>
       <c r="AB18" s="1"/>
     </row>
-    <row r="19" spans="1:28" s="45" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="87" t="s">
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="93"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93"/>
+      <c r="J19" s="93"/>
+      <c r="K19" s="93"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="O19" s="88"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="87" t="s">
+      <c r="O19" s="93"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="R19" s="88"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="87" t="s">
+      <c r="R19" s="93"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="88"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="87" t="s">
+      <c r="U19" s="93"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="25"/>
+      <c r="X19" s="93"/>
+      <c r="Y19" s="93"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="109"/>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" s="45" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
-      <c r="B20" s="39">
+      <c r="B20" s="36">
         <v>1</v>
       </c>
-      <c r="C20" s="89">
+      <c r="C20" s="94">
         <v>2</v>
       </c>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="89">
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="94">
         <v>3</v>
       </c>
-      <c r="O20" s="90"/>
-      <c r="P20" s="49"/>
-      <c r="Q20" s="91">
+      <c r="O20" s="95"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="96">
         <v>4</v>
       </c>
-      <c r="R20" s="92"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="91">
+      <c r="R20" s="97"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="96">
         <v>5</v>
       </c>
-      <c r="U20" s="92"/>
-      <c r="V20" s="51"/>
-      <c r="W20" s="91" t="s">
+      <c r="U20" s="97"/>
+      <c r="V20" s="46"/>
+      <c r="W20" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="X20" s="92"/>
-      <c r="Y20" s="92"/>
-      <c r="Z20" s="51"/>
-      <c r="AA20" s="25"/>
+      <c r="X20" s="97"/>
+      <c r="Y20" s="97"/>
+      <c r="Z20" s="46"/>
+      <c r="AA20" s="109"/>
       <c r="AB20" s="2"/>
     </row>
-    <row r="21" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="81"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="84"/>
-      <c r="W21" s="84"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="24"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="113"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80"/>
+      <c r="AA21" s="109"/>
       <c r="AB21" s="1"/>
     </row>
-    <row r="22" spans="1:28" s="45" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="62" t="s">
+      <c r="B22" s="26"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="63"/>
-      <c r="V22" s="64"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="25"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="109"/>
       <c r="AB22" s="2"/>
     </row>
-    <row r="23" spans="1:28" s="45" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="62" t="s">
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="63"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="25"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="59"/>
+      <c r="R23" s="59"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="59"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="61"/>
+      <c r="Y23" s="61"/>
+      <c r="Z23" s="61"/>
+      <c r="AA23" s="109"/>
       <c r="AB23" s="2"/>
     </row>
-    <row r="24" spans="1:28" s="45" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="62" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="63"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="64"/>
-      <c r="W24" s="65"/>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="65"/>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="25"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59"/>
+      <c r="R24" s="59"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="59"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="60"/>
+      <c r="W24" s="61"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="61"/>
+      <c r="Z24" s="61"/>
+      <c r="AA24" s="109"/>
       <c r="AB24" s="2"/>
     </row>
-    <row r="25" spans="1:28" s="45" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="25"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
+      <c r="Q25" s="106"/>
+      <c r="R25" s="106"/>
+      <c r="S25" s="106"/>
+      <c r="T25" s="106"/>
+      <c r="U25" s="106"/>
+      <c r="V25" s="106"/>
+      <c r="W25" s="106"/>
+      <c r="X25" s="106"/>
+      <c r="Y25" s="106"/>
+      <c r="Z25" s="106"/>
+      <c r="AA25" s="109"/>
       <c r="AB25" s="2"/>
     </row>
-    <row r="26" spans="1:28" s="46" customFormat="1" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14"/>
       <c r="B26" s="20"/>
       <c r="C26" s="11"/>
@@ -2837,7 +2837,7 @@
       <c r="AA26" s="16"/>
       <c r="AB26" s="10"/>
     </row>
-    <row r="27" spans="1:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21"/>
       <c r="B27" s="22"/>
       <c r="C27" s="23"/>
@@ -2864,108 +2864,112 @@
       <c r="X27" s="23"/>
       <c r="Y27" s="23"/>
       <c r="Z27" s="13"/>
-      <c r="AA27" s="24"/>
-    </row>
-    <row r="28" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+      <c r="AA27" s="108"/>
+      <c r="AB27" s="41"/>
+    </row>
+    <row r="28" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="76" t="s">
+      <c r="B28" s="24"/>
+      <c r="C28" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="76" t="s">
+      <c r="D28" s="107"/>
+      <c r="E28" s="107"/>
+      <c r="F28" s="107"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="107"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="76"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="76"/>
-      <c r="Q28" s="76"/>
-      <c r="R28" s="76"/>
-      <c r="S28" s="76"/>
-      <c r="T28" s="76"/>
-      <c r="U28" s="76"/>
-      <c r="V28" s="76"/>
-      <c r="W28" s="76"/>
-      <c r="X28" s="76"/>
-      <c r="Y28" s="76"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="24"/>
-    </row>
-    <row r="29" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+      <c r="N28" s="107"/>
+      <c r="O28" s="107"/>
+      <c r="P28" s="107"/>
+      <c r="Q28" s="107"/>
+      <c r="R28" s="107"/>
+      <c r="S28" s="107"/>
+      <c r="T28" s="107"/>
+      <c r="U28" s="107"/>
+      <c r="V28" s="107"/>
+      <c r="W28" s="107"/>
+      <c r="X28" s="107"/>
+      <c r="Y28" s="107"/>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="109"/>
+      <c r="AB28" s="41"/>
+    </row>
+    <row r="29" spans="1:28" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="71" t="s">
+      <c r="C29" s="103"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="103"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="71"/>
-      <c r="S29" s="71"/>
-      <c r="T29" s="71"/>
-      <c r="U29" s="71"/>
-      <c r="V29" s="71"/>
-      <c r="W29" s="71"/>
-      <c r="X29" s="71"/>
-      <c r="Y29" s="71"/>
-      <c r="Z29" s="32"/>
-      <c r="AA29" s="58"/>
-    </row>
-    <row r="30" spans="1:28" ht="15" x14ac:dyDescent="0.25">
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="102"/>
+      <c r="U29" s="102"/>
+      <c r="V29" s="102"/>
+      <c r="W29" s="102"/>
+      <c r="X29" s="102"/>
+      <c r="Y29" s="102"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="109"/>
+      <c r="AB29" s="41"/>
+    </row>
+    <row r="30" spans="1:28" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
-      <c r="B30" s="71" t="s">
+      <c r="B30" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="71" t="s">
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="103"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="71"/>
-      <c r="V30" s="71"/>
-      <c r="W30" s="71"/>
-      <c r="X30" s="71"/>
-      <c r="Y30" s="71"/>
-      <c r="Z30" s="71"/>
-      <c r="AA30" s="24"/>
-    </row>
-    <row r="31" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="102"/>
+      <c r="S30" s="102"/>
+      <c r="T30" s="102"/>
+      <c r="U30" s="102"/>
+      <c r="V30" s="102"/>
+      <c r="W30" s="102"/>
+      <c r="X30" s="102"/>
+      <c r="Y30" s="102"/>
+      <c r="Z30" s="102"/>
+      <c r="AA30" s="109"/>
+      <c r="AB30" s="41"/>
+    </row>
+    <row r="31" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
@@ -2981,28 +2985,29 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="102" t="s">
+      <c r="P31" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="Q31" s="103"/>
-      <c r="R31" s="103"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="108"/>
-      <c r="U31" s="108"/>
-      <c r="V31" s="108"/>
-      <c r="W31" s="108"/>
-      <c r="X31" s="108"/>
-      <c r="Y31" s="109"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="69"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="74"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="74"/>
+      <c r="X31" s="74"/>
+      <c r="Y31" s="75"/>
       <c r="Z31" s="4"/>
-      <c r="AA31" s="24"/>
-    </row>
-    <row r="32" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA31" s="109"/>
+      <c r="AB31" s="41"/>
+    </row>
+    <row r="32" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
-      <c r="B32" s="94"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="94"/>
+      <c r="B32" s="99"/>
+      <c r="C32" s="99"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -3012,28 +3017,29 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="104" t="s">
+      <c r="P32" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="Q32" s="105"/>
-      <c r="R32" s="105"/>
-      <c r="S32" s="57"/>
-      <c r="T32" s="110"/>
-      <c r="U32" s="110"/>
-      <c r="V32" s="110"/>
-      <c r="W32" s="110"/>
-      <c r="X32" s="110"/>
-      <c r="Y32" s="111"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="71"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="76"/>
+      <c r="U32" s="76"/>
+      <c r="V32" s="76"/>
+      <c r="W32" s="76"/>
+      <c r="X32" s="76"/>
+      <c r="Y32" s="77"/>
       <c r="Z32" s="4"/>
-      <c r="AA32" s="24"/>
-    </row>
-    <row r="33" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="AA32" s="109"/>
+      <c r="AB32" s="41"/>
+    </row>
+    <row r="33" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94"/>
+      <c r="B33" s="99"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -3043,165 +3049,187 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="106" t="s">
+      <c r="P33" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="Q33" s="107"/>
-      <c r="R33" s="107"/>
-      <c r="S33" s="54"/>
-      <c r="T33" s="112"/>
-      <c r="U33" s="112"/>
-      <c r="V33" s="112"/>
-      <c r="W33" s="112"/>
-      <c r="X33" s="112"/>
-      <c r="Y33" s="113"/>
+      <c r="Q33" s="73"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
+      <c r="Y33" s="63"/>
       <c r="Z33" s="4"/>
-      <c r="AA33" s="24"/>
-    </row>
-    <row r="34" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="AA33" s="109"/>
+      <c r="AB33" s="41"/>
+    </row>
+    <row r="34" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
-      <c r="B34" s="44" t="s">
+      <c r="B34" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="61"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="94"/>
-      <c r="J34" s="94"/>
-      <c r="K34" s="94"/>
-      <c r="L34" s="94"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="94"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="99"/>
+      <c r="K34" s="99"/>
+      <c r="L34" s="99"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="73"/>
+      <c r="R34" s="104"/>
+      <c r="S34" s="104"/>
+      <c r="T34" s="104"/>
+      <c r="U34" s="104"/>
+      <c r="V34" s="104"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
-      <c r="AA34" s="24"/>
-    </row>
-    <row r="35" spans="1:27" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="AA34" s="109"/>
+      <c r="AB34" s="41"/>
+    </row>
+    <row r="35" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
-      <c r="B35" s="44" t="s">
+      <c r="B35" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
       <c r="M35" s="12"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
       <c r="P35" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R35" s="60"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="95"/>
-      <c r="V35" s="95"/>
-      <c r="W35" s="95"/>
-      <c r="X35" s="95"/>
-      <c r="Y35" s="95"/>
+      <c r="Q35" s="41"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="100"/>
+      <c r="V35" s="100"/>
+      <c r="W35" s="100"/>
+      <c r="X35" s="100"/>
+      <c r="Y35" s="100"/>
       <c r="Z35" s="4"/>
-      <c r="AA35" s="24"/>
-    </row>
-    <row r="36" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA35" s="109"/>
+      <c r="AB35" s="41"/>
+    </row>
+    <row r="36" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
-      <c r="S36" s="70"/>
-      <c r="T36" s="70"/>
-      <c r="U36" s="70"/>
-      <c r="V36" s="70"/>
-      <c r="W36" s="70"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="101"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="101"/>
+      <c r="J36" s="101"/>
+      <c r="K36" s="101"/>
+      <c r="L36" s="101"/>
+      <c r="M36" s="101"/>
+      <c r="N36" s="101"/>
+      <c r="O36" s="101"/>
+      <c r="P36" s="101"/>
+      <c r="Q36" s="101"/>
+      <c r="R36" s="101"/>
+      <c r="S36" s="101"/>
+      <c r="T36" s="101"/>
+      <c r="U36" s="101"/>
+      <c r="V36" s="101"/>
+      <c r="W36" s="101"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
-      <c r="AA36" s="24"/>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A37" s="59"/>
-      <c r="B37" s="93"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
-      <c r="O37" s="93"/>
-      <c r="P37" s="93"/>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="93"/>
-      <c r="S37" s="93"/>
-      <c r="T37" s="93"/>
-      <c r="U37" s="93"/>
-      <c r="V37" s="93"/>
-      <c r="W37" s="93"/>
-      <c r="X37" s="93"/>
-      <c r="Y37" s="93"/>
-      <c r="Z37" s="55"/>
-      <c r="AA37" s="56"/>
+      <c r="AA36" s="109"/>
+      <c r="AB36" s="41"/>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" s="53"/>
+      <c r="B37" s="98"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="98"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="98"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="98"/>
+      <c r="N37" s="98"/>
+      <c r="O37" s="98"/>
+      <c r="P37" s="98"/>
+      <c r="Q37" s="98"/>
+      <c r="R37" s="98"/>
+      <c r="S37" s="98"/>
+      <c r="T37" s="98"/>
+      <c r="U37" s="98"/>
+      <c r="V37" s="98"/>
+      <c r="W37" s="98"/>
+      <c r="X37" s="98"/>
+      <c r="Y37" s="98"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="51"/>
+      <c r="AB37" s="41"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="74">
-    <mergeCell ref="T33:Y33"/>
+  <mergeCells count="77">
+    <mergeCell ref="AA27:AA36"/>
+    <mergeCell ref="AA7:AA25"/>
+    <mergeCell ref="AA1:AA6"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="S6:Y6"/>
     <mergeCell ref="D6:N6"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G12:Y12"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:Z15"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="C21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="D4:Y4"/>
+    <mergeCell ref="D10:R10"/>
+    <mergeCell ref="U17:Y17"/>
     <mergeCell ref="B37:Y37"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="U35:Y35"/>
-    <mergeCell ref="D4:Y4"/>
-    <mergeCell ref="D10:R10"/>
-    <mergeCell ref="U17:Y17"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="W8:Y8"/>
-    <mergeCell ref="D7:R7"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="N22:V22"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="C36:W36"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="M30:Z30"/>
+    <mergeCell ref="R34:V34"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="M25:Z25"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="M28:Y28"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="N29:Y29"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:Y14"/>
     <mergeCell ref="B1:Y1"/>
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C20:K20"/>
@@ -3218,48 +3246,36 @@
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="Q5:U5"/>
-    <mergeCell ref="N22:V22"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:Z13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:Y14"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="G12:Y12"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:Z15"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="C21:M21"/>
-    <mergeCell ref="N21:P21"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="T21:V21"/>
     <mergeCell ref="W21:Z21"/>
-    <mergeCell ref="C36:W36"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="M30:Z30"/>
-    <mergeCell ref="R34:V34"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="M25:Z25"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="M28:Y28"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="N29:Y29"/>
+    <mergeCell ref="D7:R7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:Z13"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="N24:V24"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="T33:Y33"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="N23:V23"/>
+    <mergeCell ref="W23:Z23"/>
     <mergeCell ref="P31:R31"/>
     <mergeCell ref="P32:R32"/>
     <mergeCell ref="P33:R33"/>
     <mergeCell ref="T31:Y31"/>
     <mergeCell ref="T32:Y32"/>
-    <mergeCell ref="N24:V24"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="N23:V23"/>
-    <mergeCell ref="W23:Z23"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.11811023622047245" bottom="0.15748031496062992" header="5.2362204724409454" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/resources/report/60/95/einvoices_template/ParisVN_CNHN/ParisVN_CNHN_1.xlsx
+++ b/resources/report/60/95/einvoices_template/ParisVN_CNHN/ParisVN_CNHN_1.xlsx
@@ -1456,6 +1456,54 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1468,6 +1516,75 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1515,123 +1632,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1989,32 +1989,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="16.5" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21"/>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
+      <c r="B1" s="84"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
+      <c r="U1" s="85"/>
+      <c r="V1" s="85"/>
+      <c r="W1" s="85"/>
+      <c r="X1" s="85"/>
+      <c r="Y1" s="85"/>
       <c r="Z1" s="22"/>
-      <c r="AA1" s="108"/>
+      <c r="AA1" s="58"/>
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2044,7 +2044,7 @@
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="109"/>
+      <c r="AA2" s="59"/>
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2054,61 +2054,61 @@
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79"/>
-      <c r="Q3" s="79"/>
-      <c r="R3" s="79"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="79"/>
-      <c r="U3" s="79"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
       <c r="V3" s="56"/>
       <c r="W3" s="56"/>
       <c r="X3" s="56"/>
       <c r="Y3" s="56"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="109"/>
+      <c r="AA3" s="59"/>
       <c r="AB3" s="1"/>
     </row>
     <row r="4" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14"/>
-      <c r="B4" s="79" t="s">
+      <c r="B4" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
-      <c r="T4" s="116"/>
-      <c r="U4" s="116"/>
-      <c r="V4" s="116"/>
-      <c r="W4" s="116"/>
-      <c r="X4" s="116"/>
-      <c r="Y4" s="116"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="70"/>
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
+      <c r="Y4" s="70"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="109"/>
+      <c r="AA4" s="59"/>
       <c r="AB4" s="1"/>
     </row>
     <row r="5" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2117,32 +2117,32 @@
         <v>40</v>
       </c>
       <c r="C5" s="56"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
       <c r="L5" s="56"/>
       <c r="M5" s="56"/>
-      <c r="N5" s="78" t="s">
+      <c r="N5" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="78"/>
+      <c r="O5" s="93"/>
       <c r="P5" s="56"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="79"/>
-      <c r="U5" s="79"/>
+      <c r="Q5" s="92"/>
+      <c r="R5" s="92"/>
+      <c r="S5" s="92"/>
+      <c r="T5" s="92"/>
+      <c r="U5" s="92"/>
       <c r="V5" s="56"/>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="56"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="109"/>
+      <c r="AA5" s="59"/>
       <c r="AB5" s="1"/>
     </row>
     <row r="6" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2151,98 +2151,98 @@
         <v>42</v>
       </c>
       <c r="C6" s="57"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="111"/>
-      <c r="K6" s="111"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="62"/>
       <c r="O6" s="57" t="s">
         <v>41</v>
       </c>
       <c r="P6" s="57"/>
       <c r="Q6" s="57"/>
       <c r="R6" s="57"/>
-      <c r="S6" s="111"/>
-      <c r="T6" s="111"/>
-      <c r="U6" s="111"/>
-      <c r="V6" s="111"/>
-      <c r="W6" s="111"/>
-      <c r="X6" s="111"/>
-      <c r="Y6" s="111"/>
+      <c r="S6" s="62"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="62"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
       <c r="Z6" s="20"/>
-      <c r="AA6" s="110"/>
+      <c r="AA6" s="60"/>
       <c r="AB6" s="1"/>
     </row>
     <row r="7" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81"/>
-      <c r="P7" s="81"/>
-      <c r="Q7" s="81"/>
-      <c r="R7" s="81"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="82"/>
-      <c r="Z7" s="82"/>
-      <c r="AA7" s="108"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="58"/>
       <c r="AB7" s="1"/>
     </row>
     <row r="8" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="87" t="s">
+      <c r="D8" s="98" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
-      <c r="N8" s="87"/>
-      <c r="O8" s="87"/>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="88" t="s">
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="T8" s="88"/>
-      <c r="U8" s="88"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
+      <c r="T8" s="99"/>
+      <c r="U8" s="99"/>
+      <c r="V8" s="99"/>
+      <c r="W8" s="100"/>
+      <c r="X8" s="100"/>
+      <c r="Y8" s="100"/>
       <c r="Z8" s="24"/>
-      <c r="AA8" s="109"/>
+      <c r="AA8" s="59"/>
       <c r="AB8" s="1"/>
     </row>
     <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2266,49 +2266,49 @@
       <c r="P9" s="47"/>
       <c r="Q9" s="47"/>
       <c r="R9" s="47"/>
-      <c r="S9" s="82" t="s">
+      <c r="S9" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="T9" s="82"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="86"/>
-      <c r="W9" s="86"/>
-      <c r="X9" s="86"/>
-      <c r="Y9" s="86"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="97"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="97"/>
+      <c r="Y9" s="97"/>
       <c r="Z9" s="24"/>
-      <c r="AA9" s="109"/>
+      <c r="AA9" s="59"/>
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="85" t="s">
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="85"/>
-      <c r="U10" s="85"/>
-      <c r="V10" s="85"/>
-      <c r="W10" s="85"/>
-      <c r="X10" s="85"/>
-      <c r="Y10" s="85"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="96"/>
+      <c r="V10" s="96"/>
+      <c r="W10" s="96"/>
+      <c r="X10" s="96"/>
+      <c r="Y10" s="96"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="109"/>
+      <c r="AA10" s="59"/>
       <c r="AB10" s="1"/>
     </row>
     <row r="11" spans="1:28" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2338,135 +2338,135 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="109"/>
+      <c r="AA11" s="59"/>
       <c r="AB11" s="1"/>
     </row>
     <row r="12" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="82"/>
-      <c r="T12" s="82"/>
-      <c r="U12" s="82"/>
-      <c r="V12" s="82"/>
-      <c r="W12" s="82"/>
-      <c r="X12" s="82"/>
-      <c r="Y12" s="82"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
       <c r="Z12" s="24"/>
-      <c r="AA12" s="109"/>
+      <c r="AA12" s="59"/>
       <c r="AB12" s="1"/>
     </row>
     <row r="13" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="84"/>
-      <c r="P13" s="84"/>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="84"/>
-      <c r="S13" s="84"/>
-      <c r="T13" s="84"/>
-      <c r="U13" s="84"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="84"/>
-      <c r="X13" s="84"/>
-      <c r="Y13" s="84"/>
-      <c r="Z13" s="84"/>
-      <c r="AA13" s="109"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="59"/>
       <c r="AB13" s="1"/>
     </row>
     <row r="14" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="83"/>
-      <c r="U14" s="83"/>
-      <c r="V14" s="83"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="83"/>
-      <c r="Y14" s="83"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="63"/>
+      <c r="W14" s="63"/>
+      <c r="X14" s="63"/>
+      <c r="Y14" s="63"/>
       <c r="Z14" s="24"/>
-      <c r="AA14" s="109"/>
+      <c r="AA14" s="59"/>
       <c r="AB14" s="1"/>
     </row>
     <row r="15" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
-      <c r="B15" s="83" t="s">
+      <c r="B15" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="109"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
+      <c r="Q15" s="65"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="65"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="59"/>
       <c r="AB15" s="1"/>
     </row>
     <row r="16" spans="1:28" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2496,7 +2496,7 @@
       <c r="X16" s="33"/>
       <c r="Y16" s="33"/>
       <c r="Z16" s="24"/>
-      <c r="AA16" s="109"/>
+      <c r="AA16" s="59"/>
       <c r="AB16" s="1"/>
     </row>
     <row r="17" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2511,8 +2511,8 @@
       <c r="G17" s="34"/>
       <c r="H17" s="34"/>
       <c r="I17" s="34"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
       <c r="L17" s="34"/>
       <c r="M17" s="40" t="s">
         <v>25</v>
@@ -2524,13 +2524,13 @@
       <c r="R17" s="40"/>
       <c r="S17" s="40"/>
       <c r="T17" s="40"/>
-      <c r="U17" s="82"/>
-      <c r="V17" s="82"/>
-      <c r="W17" s="82"/>
-      <c r="X17" s="82"/>
-      <c r="Y17" s="82"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
       <c r="Z17" s="25"/>
-      <c r="AA17" s="109"/>
+      <c r="AA17" s="59"/>
       <c r="AB17" s="1"/>
     </row>
     <row r="18" spans="1:28" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2560,7 +2560,7 @@
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
-      <c r="AA18" s="109"/>
+      <c r="AA18" s="59"/>
       <c r="AB18" s="1"/>
     </row>
     <row r="19" spans="1:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2568,41 +2568,41 @@
       <c r="B19" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="93"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="87"/>
+      <c r="K19" s="87"/>
       <c r="L19" s="42"/>
       <c r="M19" s="43"/>
-      <c r="N19" s="92" t="s">
+      <c r="N19" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="O19" s="93"/>
+      <c r="O19" s="87"/>
       <c r="P19" s="43"/>
-      <c r="Q19" s="92" t="s">
+      <c r="Q19" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="R19" s="93"/>
+      <c r="R19" s="87"/>
       <c r="S19" s="43"/>
-      <c r="T19" s="92" t="s">
+      <c r="T19" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="93"/>
+      <c r="U19" s="87"/>
       <c r="V19" s="43"/>
-      <c r="W19" s="92" t="s">
+      <c r="W19" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="X19" s="93"/>
-      <c r="Y19" s="93"/>
+      <c r="X19" s="87"/>
+      <c r="Y19" s="87"/>
       <c r="Z19" s="43"/>
-      <c r="AA19" s="109"/>
+      <c r="AA19" s="59"/>
       <c r="AB19" s="2"/>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2610,71 +2610,71 @@
       <c r="B20" s="36">
         <v>1</v>
       </c>
-      <c r="C20" s="94">
+      <c r="C20" s="88">
         <v>2</v>
       </c>
-      <c r="D20" s="95"/>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="95"/>
-      <c r="H20" s="95"/>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
       <c r="L20" s="45"/>
       <c r="M20" s="44"/>
-      <c r="N20" s="94">
+      <c r="N20" s="88">
         <v>3</v>
       </c>
-      <c r="O20" s="95"/>
+      <c r="O20" s="89"/>
       <c r="P20" s="44"/>
-      <c r="Q20" s="96">
+      <c r="Q20" s="90">
         <v>4</v>
       </c>
-      <c r="R20" s="97"/>
+      <c r="R20" s="91"/>
       <c r="S20" s="46"/>
-      <c r="T20" s="96">
+      <c r="T20" s="90">
         <v>5</v>
       </c>
-      <c r="U20" s="97"/>
+      <c r="U20" s="91"/>
       <c r="V20" s="46"/>
-      <c r="W20" s="96" t="s">
+      <c r="W20" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="X20" s="97"/>
-      <c r="Y20" s="97"/>
+      <c r="X20" s="91"/>
+      <c r="Y20" s="91"/>
       <c r="Z20" s="46"/>
-      <c r="AA20" s="109"/>
+      <c r="AA20" s="59"/>
       <c r="AB20" s="2"/>
     </row>
     <row r="21" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
       <c r="B21" s="37"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="113"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="113"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="114"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="109"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
+      <c r="X21" s="94"/>
+      <c r="Y21" s="94"/>
+      <c r="Z21" s="94"/>
+      <c r="AA21" s="59"/>
       <c r="AB21" s="1"/>
     </row>
     <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2691,56 +2691,56 @@
       <c r="K22" s="32"/>
       <c r="L22" s="32"/>
       <c r="M22" s="32"/>
-      <c r="N22" s="58" t="s">
+      <c r="N22" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="61"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="61"/>
-      <c r="Z22" s="61"/>
-      <c r="AA22" s="109"/>
+      <c r="O22" s="75"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="75"/>
+      <c r="T22" s="75"/>
+      <c r="U22" s="75"/>
+      <c r="V22" s="76"/>
+      <c r="W22" s="77"/>
+      <c r="X22" s="77"/>
+      <c r="Y22" s="77"/>
+      <c r="Z22" s="77"/>
+      <c r="AA22" s="59"/>
       <c r="AB22" s="2"/>
     </row>
     <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18"/>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="106"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="27"/>
       <c r="L23" s="27"/>
       <c r="M23" s="27"/>
-      <c r="N23" s="58" t="s">
+      <c r="N23" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="O23" s="59"/>
-      <c r="P23" s="59"/>
-      <c r="Q23" s="59"/>
-      <c r="R23" s="59"/>
-      <c r="S23" s="59"/>
-      <c r="T23" s="59"/>
-      <c r="U23" s="59"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
-      <c r="Z23" s="61"/>
-      <c r="AA23" s="109"/>
+      <c r="O23" s="75"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="75"/>
+      <c r="S23" s="75"/>
+      <c r="T23" s="75"/>
+      <c r="U23" s="75"/>
+      <c r="V23" s="76"/>
+      <c r="W23" s="77"/>
+      <c r="X23" s="77"/>
+      <c r="Y23" s="77"/>
+      <c r="Z23" s="77"/>
+      <c r="AA23" s="59"/>
       <c r="AB23" s="2"/>
     </row>
     <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2757,54 +2757,54 @@
       <c r="K24" s="27"/>
       <c r="L24" s="27"/>
       <c r="M24" s="27"/>
-      <c r="N24" s="58" t="s">
+      <c r="N24" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="O24" s="59"/>
-      <c r="P24" s="59"/>
-      <c r="Q24" s="59"/>
-      <c r="R24" s="59"/>
-      <c r="S24" s="59"/>
-      <c r="T24" s="59"/>
-      <c r="U24" s="59"/>
-      <c r="V24" s="60"/>
-      <c r="W24" s="61"/>
-      <c r="X24" s="61"/>
-      <c r="Y24" s="61"/>
-      <c r="Z24" s="61"/>
-      <c r="AA24" s="109"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="75"/>
+      <c r="T24" s="75"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="76"/>
+      <c r="W24" s="77"/>
+      <c r="X24" s="77"/>
+      <c r="Y24" s="77"/>
+      <c r="Z24" s="77"/>
+      <c r="AA24" s="59"/>
       <c r="AB24" s="2"/>
     </row>
     <row r="25" spans="1:28" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
-      <c r="B25" s="105" t="s">
+      <c r="B25" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="105"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="81"/>
       <c r="L25" s="38"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="106"/>
-      <c r="T25" s="106"/>
-      <c r="U25" s="106"/>
-      <c r="V25" s="106"/>
-      <c r="W25" s="106"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="106"/>
-      <c r="Z25" s="106"/>
-      <c r="AA25" s="109"/>
+      <c r="M25" s="82"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82"/>
+      <c r="R25" s="82"/>
+      <c r="S25" s="82"/>
+      <c r="T25" s="82"/>
+      <c r="U25" s="82"/>
+      <c r="V25" s="82"/>
+      <c r="W25" s="82"/>
+      <c r="X25" s="82"/>
+      <c r="Y25" s="82"/>
+      <c r="Z25" s="82"/>
+      <c r="AA25" s="59"/>
       <c r="AB25" s="2"/>
     </row>
     <row r="26" spans="1:28" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2864,109 +2864,109 @@
       <c r="X27" s="23"/>
       <c r="Y27" s="23"/>
       <c r="Z27" s="13"/>
-      <c r="AA27" s="108"/>
+      <c r="AA27" s="58"/>
       <c r="AB27" s="41"/>
     </row>
     <row r="28" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
       <c r="B28" s="24"/>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="107"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="107"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
       <c r="K28" s="29"/>
       <c r="L28" s="29"/>
-      <c r="M28" s="107" t="s">
+      <c r="M28" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="107"/>
-      <c r="O28" s="107"/>
-      <c r="P28" s="107"/>
-      <c r="Q28" s="107"/>
-      <c r="R28" s="107"/>
-      <c r="S28" s="107"/>
-      <c r="T28" s="107"/>
-      <c r="U28" s="107"/>
-      <c r="V28" s="107"/>
-      <c r="W28" s="107"/>
-      <c r="X28" s="107"/>
-      <c r="Y28" s="107"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="83"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
       <c r="Z28" s="29"/>
-      <c r="AA28" s="109"/>
+      <c r="AA28" s="59"/>
       <c r="AB28" s="41"/>
     </row>
     <row r="29" spans="1:28" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="103"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="31"/>
-      <c r="N29" s="102" t="s">
+      <c r="N29" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="102"/>
-      <c r="P29" s="102"/>
-      <c r="Q29" s="102"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="102"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="102"/>
-      <c r="V29" s="102"/>
-      <c r="W29" s="102"/>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="102"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+      <c r="T29" s="71"/>
+      <c r="U29" s="71"/>
+      <c r="V29" s="71"/>
+      <c r="W29" s="71"/>
+      <c r="X29" s="71"/>
+      <c r="Y29" s="71"/>
       <c r="Z29" s="30"/>
-      <c r="AA29" s="109"/>
+      <c r="AA29" s="59"/>
       <c r="AB29" s="41"/>
     </row>
     <row r="30" spans="1:28" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
-      <c r="B30" s="102" t="s">
+      <c r="B30" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="103"/>
-      <c r="J30" s="103"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
       <c r="K30" s="29"/>
       <c r="L30" s="29"/>
-      <c r="M30" s="102" t="s">
+      <c r="M30" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="N30" s="102"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="102"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="102"/>
-      <c r="T30" s="102"/>
-      <c r="U30" s="102"/>
-      <c r="V30" s="102"/>
-      <c r="W30" s="102"/>
-      <c r="X30" s="102"/>
-      <c r="Y30" s="102"/>
-      <c r="Z30" s="102"/>
-      <c r="AA30" s="109"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="71"/>
+      <c r="V30" s="71"/>
+      <c r="W30" s="71"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="71"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="59"/>
       <c r="AB30" s="41"/>
     </row>
     <row r="31" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2985,29 +2985,29 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="68" t="s">
+      <c r="P31" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="Q31" s="69"/>
-      <c r="R31" s="69"/>
+      <c r="Q31" s="108"/>
+      <c r="R31" s="108"/>
       <c r="S31" s="48"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="75"/>
+      <c r="T31" s="113"/>
+      <c r="U31" s="113"/>
+      <c r="V31" s="113"/>
+      <c r="W31" s="113"/>
+      <c r="X31" s="113"/>
+      <c r="Y31" s="114"/>
       <c r="Z31" s="4"/>
-      <c r="AA31" s="109"/>
+      <c r="AA31" s="59"/>
       <c r="AB31" s="41"/>
     </row>
     <row r="32" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
-      <c r="B32" s="99"/>
-      <c r="C32" s="99"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -3017,29 +3017,29 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="70" t="s">
+      <c r="P32" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
+      <c r="Q32" s="110"/>
+      <c r="R32" s="110"/>
       <c r="S32" s="52"/>
-      <c r="T32" s="76"/>
-      <c r="U32" s="76"/>
-      <c r="V32" s="76"/>
-      <c r="W32" s="76"/>
-      <c r="X32" s="76"/>
-      <c r="Y32" s="77"/>
+      <c r="T32" s="115"/>
+      <c r="U32" s="115"/>
+      <c r="V32" s="115"/>
+      <c r="W32" s="115"/>
+      <c r="X32" s="115"/>
+      <c r="Y32" s="116"/>
       <c r="Z32" s="4"/>
-      <c r="AA32" s="109"/>
+      <c r="AA32" s="59"/>
       <c r="AB32" s="41"/>
     </row>
     <row r="33" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
-      <c r="B33" s="99"/>
-      <c r="C33" s="99"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -3049,20 +3049,20 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="72" t="s">
+      <c r="P33" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="Q33" s="73"/>
-      <c r="R33" s="73"/>
+      <c r="Q33" s="112"/>
+      <c r="R33" s="112"/>
       <c r="S33" s="49"/>
-      <c r="T33" s="62"/>
-      <c r="U33" s="62"/>
-      <c r="V33" s="62"/>
-      <c r="W33" s="62"/>
-      <c r="X33" s="62"/>
-      <c r="Y33" s="63"/>
+      <c r="T33" s="101"/>
+      <c r="U33" s="101"/>
+      <c r="V33" s="101"/>
+      <c r="W33" s="101"/>
+      <c r="X33" s="101"/>
+      <c r="Y33" s="102"/>
       <c r="Z33" s="4"/>
-      <c r="AA33" s="109"/>
+      <c r="AA33" s="59"/>
       <c r="AB33" s="41"/>
     </row>
     <row r="34" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
@@ -3071,30 +3071,30 @@
         <v>37</v>
       </c>
       <c r="C34" s="55"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="99"/>
-      <c r="L34" s="99"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="61"/>
+      <c r="J34" s="61"/>
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
-      <c r="R34" s="104"/>
-      <c r="S34" s="104"/>
-      <c r="T34" s="104"/>
-      <c r="U34" s="104"/>
-      <c r="V34" s="104"/>
+      <c r="R34" s="80"/>
+      <c r="S34" s="80"/>
+      <c r="T34" s="80"/>
+      <c r="U34" s="80"/>
+      <c r="V34" s="80"/>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
-      <c r="AA34" s="109"/>
+      <c r="AA34" s="59"/>
       <c r="AB34" s="41"/>
     </row>
     <row r="35" spans="1:28" ht="16.8" x14ac:dyDescent="0.3">
@@ -3122,73 +3122,73 @@
       <c r="R35" s="54"/>
       <c r="S35" s="29"/>
       <c r="T35" s="29"/>
-      <c r="U35" s="100"/>
-      <c r="V35" s="100"/>
-      <c r="W35" s="100"/>
-      <c r="X35" s="100"/>
-      <c r="Y35" s="100"/>
+      <c r="U35" s="73"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="73"/>
+      <c r="Y35" s="73"/>
       <c r="Z35" s="4"/>
-      <c r="AA35" s="109"/>
+      <c r="AA35" s="59"/>
       <c r="AB35" s="41"/>
     </row>
     <row r="36" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="10"/>
-      <c r="C36" s="101" t="s">
+      <c r="C36" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="101"/>
-      <c r="H36" s="101"/>
-      <c r="I36" s="101"/>
-      <c r="J36" s="101"/>
-      <c r="K36" s="101"/>
-      <c r="L36" s="101"/>
-      <c r="M36" s="101"/>
-      <c r="N36" s="101"/>
-      <c r="O36" s="101"/>
-      <c r="P36" s="101"/>
-      <c r="Q36" s="101"/>
-      <c r="R36" s="101"/>
-      <c r="S36" s="101"/>
-      <c r="T36" s="101"/>
-      <c r="U36" s="101"/>
-      <c r="V36" s="101"/>
-      <c r="W36" s="101"/>
+      <c r="D36" s="78"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="78"/>
+      <c r="M36" s="78"/>
+      <c r="N36" s="78"/>
+      <c r="O36" s="78"/>
+      <c r="P36" s="78"/>
+      <c r="Q36" s="78"/>
+      <c r="R36" s="78"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="78"/>
+      <c r="U36" s="78"/>
+      <c r="V36" s="78"/>
+      <c r="W36" s="78"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
-      <c r="AA36" s="109"/>
+      <c r="AA36" s="59"/>
       <c r="AB36" s="41"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="53"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="98"/>
-      <c r="G37" s="98"/>
-      <c r="H37" s="98"/>
-      <c r="I37" s="98"/>
-      <c r="J37" s="98"/>
-      <c r="K37" s="98"/>
-      <c r="L37" s="98"/>
-      <c r="M37" s="98"/>
-      <c r="N37" s="98"/>
-      <c r="O37" s="98"/>
-      <c r="P37" s="98"/>
-      <c r="Q37" s="98"/>
-      <c r="R37" s="98"/>
-      <c r="S37" s="98"/>
-      <c r="T37" s="98"/>
-      <c r="U37" s="98"/>
-      <c r="V37" s="98"/>
-      <c r="W37" s="98"/>
-      <c r="X37" s="98"/>
-      <c r="Y37" s="98"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="72"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="72"/>
+      <c r="T37" s="72"/>
+      <c r="U37" s="72"/>
+      <c r="V37" s="72"/>
+      <c r="W37" s="72"/>
+      <c r="X37" s="72"/>
+      <c r="Y37" s="72"/>
       <c r="Z37" s="50"/>
       <c r="AA37" s="51"/>
       <c r="AB37" s="41"/>
@@ -3196,6 +3196,67 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="77">
+    <mergeCell ref="N24:V24"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="T33:Y33"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="N23:V23"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="P31:R31"/>
+    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="P33:R33"/>
+    <mergeCell ref="T31:Y31"/>
+    <mergeCell ref="T32:Y32"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="Q5:U5"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="W21:Z21"/>
+    <mergeCell ref="D7:R7"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:Z13"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="D8:R8"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:Y14"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="C20:K20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="W19:Y19"/>
+    <mergeCell ref="W20:Y20"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="B37:Y37"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="U35:Y35"/>
+    <mergeCell ref="N22:V22"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="C36:W36"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="M30:Z30"/>
+    <mergeCell ref="R34:V34"/>
+    <mergeCell ref="B25:K25"/>
+    <mergeCell ref="M25:Z25"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="M28:Y28"/>
+    <mergeCell ref="D34:O34"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="N29:Y29"/>
     <mergeCell ref="AA27:AA36"/>
     <mergeCell ref="AA7:AA25"/>
     <mergeCell ref="AA1:AA6"/>
@@ -3212,70 +3273,9 @@
     <mergeCell ref="D4:Y4"/>
     <mergeCell ref="D10:R10"/>
     <mergeCell ref="U17:Y17"/>
-    <mergeCell ref="B37:Y37"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="U35:Y35"/>
-    <mergeCell ref="N22:V22"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="C36:W36"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="M30:Z30"/>
-    <mergeCell ref="R34:V34"/>
-    <mergeCell ref="B25:K25"/>
-    <mergeCell ref="M25:Z25"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="M28:Y28"/>
-    <mergeCell ref="D34:O34"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="N29:Y29"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:Y14"/>
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="C20:K20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="W19:Y19"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="Q5:U5"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="T21:V21"/>
-    <mergeCell ref="W21:Z21"/>
-    <mergeCell ref="D7:R7"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:Z13"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="D8:R8"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="W8:Y8"/>
-    <mergeCell ref="N24:V24"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="T33:Y33"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="N23:V23"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="P31:R31"/>
-    <mergeCell ref="P32:R32"/>
-    <mergeCell ref="P33:R33"/>
-    <mergeCell ref="T31:Y31"/>
-    <mergeCell ref="T32:Y32"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.11811023622047245" bottom="0.15748031496062992" header="5.2362204724409454" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="90" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>